--- a/out_blind/cable_list_RK1.xlsx
+++ b/out_blind/cable_list_RK1.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -558,7 +558,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X2X0,8 2501 MT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -580,7 +580,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -604,7 +604,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -626,7 +626,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK AFG CCA 3X2X0,8 MT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -648,7 +648,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 5X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X2X0,8 2501 MT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -685,14 +685,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VAV-01 Sturing VAV-retour [?]</t>
+          <t>TT-11 Ruimtetemperatuur</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -707,14 +707,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EH-01 Sturing + storing elektrische radiator 1</t>
+          <t>VAV-01 Sturing VAV-retour [?]</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -729,14 +729,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EH-02 Sturing + storing elektrische radiator 2</t>
+          <t>EH-01 Sturing + storing elektrische radiator 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -751,14 +751,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EH-03 Sturing storing elektrische radiator 3</t>
+          <t>EH-02 Sturing + storing elektrische radiator 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -773,14 +773,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EH-04 Sturing + storing elektrische naverwarmer</t>
+          <t>EH-03 Sturing storing elektrische radiator 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -795,14 +795,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKT-01 Brandklep toevoer [?]</t>
+          <t>EH-04 Sturing + storing elektrische naverwarmer</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -817,14 +817,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKA-01 Brandklep afvoer [?]</t>
+          <t>BKT-01 Brandklep toevoer [?]</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -839,14 +839,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NSA-01 Toevoerluchtklep 1 [?]</t>
+          <t>BKA-01 Brandklep afvoer [?]</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NSA-02 Toevoerluchtklep 2 [?]</t>
+          <t>NSA-01 Toevoerluchtklep 1 [?]</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -883,14 +883,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EH-01 Sturing + storing elektrische radiator 1</t>
+          <t>NSA-02 Toevoerluchtklep 2 [?]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -905,14 +905,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EH-01 Sturing + storing elektrische radiator 2</t>
+          <t>TT-11 Ruimtetemperatuur</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -927,14 +927,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EH-01 Sturing + storing elektrische radiator 3</t>
+          <t>EH-01 Sturing + storing elektrische radiator 1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -949,14 +949,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EH-01 Sturing + storing elektrische radiator 4</t>
+          <t>EH-01 Sturing + storing elektrische radiator 2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -971,21 +971,19 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KVT-02 Toevoerventilator voeding</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
+          <t>EH-01 Sturing + storing elektrische radiator 3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>?kW/9A/230V</t>
+          <t>in TR</t>
         </is>
       </c>
     </row>
@@ -995,14 +993,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KVT-02 Toevoerventilator</t>
+          <t>EH-01 Sturing + storing elektrische radiator 4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1017,19 +1015,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PT-01 Inblaasdruk</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
+          <t>KVT-02 Toevoerventilator voeding</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 5X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>in TR</t>
+          <t>?kW/9A/230V</t>
         </is>
       </c>
     </row>
@@ -1039,14 +1039,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EH-01 Sturing + storing elektrische radiator LS-ruimte</t>
+          <t>KVT-02 Toevoerventilator</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK AFG CCA 3X2X0,8 MT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1061,14 +1061,14 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EH-01 Sturing storing elektrische radiator 1</t>
+          <t>PT-01 Inblaasdruk</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1083,14 +1083,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EH-02 Sturing + storing elektrische radiator 2</t>
+          <t>TT-11 Ruimtetemperatuur LS-ruimte K1-005</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1105,14 +1105,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EH-03 + storing elektrische radiator 3</t>
+          <t>TT-12 Ruimtetemperatuur schakelverdeelruimte K1-006</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1127,14 +1127,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EH-04 Sturing storing elektrische radiator 4</t>
+          <t>TT-13 Ruimtetemperatuur traforuimte 1 K1-008</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1149,21 +1149,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KVT-02 Toevoerventilator voeding</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
+          <t>TT-14 Ruimtetemperatuur 2 K1-007</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>?kW/9A/230V</t>
+          <t>in TR</t>
         </is>
       </c>
     </row>
@@ -1173,14 +1171,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KVT-02 Toevoerventilator</t>
+          <t>EH-01 Sturing + storing elektrische radiator LS-ruimte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1195,14 +1193,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PT-01 Inblaasdruk</t>
+          <t>EH-01 Sturing storing elektrische radiator 1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 5X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1217,14 +1215,14 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EH-01 Sturing storing elektrische radiator LS-ruimte</t>
+          <t>EH-02 Sturing + storing elektrische radiator 2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1239,14 +1237,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BKT-01 Brandklep centrale toevoer [?]</t>
+          <t>EH-03 + storing elektrische radiator 3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1261,14 +1259,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BKT-02 Brandklep toevoer LS-ruimte K1-005 [?]</t>
+          <t>EH-04 Sturing storing elektrische radiator 4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1283,19 +1281,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BKT-03 Brandklep toevoer schakelverdeelruimte K1-006 [?]</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>KVT-02 Toevoerventilator voeding</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>in TR</t>
+          <t>?kW/9A/230V</t>
         </is>
       </c>
     </row>
@@ -1305,14 +1305,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BKT-04 Brandklep toevoer traforuimte 1 K1-008 [?]</t>
+          <t>KVT-02 Toevoerventilator</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK AFG CCA 3X2X0,8 MT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1327,14 +1327,14 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BKT-05 Brandklep toevoer traforuimte 2 K1-007 [?]</t>
+          <t>PT-01 Inblaasdruk</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1349,14 +1349,14 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BKA-01 Brandklep centrale retour [?]</t>
+          <t>TT-11 Ruimtetemperatuur LS-ruimte K1-005</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BKA-02 Brandklep retour LS-ruimte K1-005 [?]</t>
+          <t>TT-12 Ruimtetemperatuur schakelverdeelruimte K1-006</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1393,14 +1393,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BKA-03 Brandklep retour schakelverdeelruimte K1-006 [?]</t>
+          <t>TT-13 Ruimtetemperatuur traforuimte 1 K1-008</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1415,14 +1415,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BKA-04 Brandklep retour traforuimte 1 K1-008 [?]</t>
+          <t>TT-14 Ruimtetemperatuur traforuimte 2 K1-007</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1437,14 +1437,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BKA-05 Brandklep retour traforuimte 2 K1-007 [?]</t>
+          <t>EH-01 Sturing storing elektrische radiator LS-ruimte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHJZ 7X1 MT</t>
+          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1459,16 +1459,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>VWP-01 Vuilwaterpomp 1 voeding</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>1</v>
-      </c>
+          <t>BKT-01 Brandklep centrale toevoer [?]</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1483,14 +1481,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>VWP-01 Vuilwaterpomp 1</t>
+          <t>BKT-02 Brandklep toevoer LS-ruimte K1-005 [?]</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1505,14 +1503,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VWP-01 Vuilwaterpomp 1</t>
+          <t>BKT-03 Brandklep toevoer schakelverdeelruimte K1-006 [?]</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1527,14 +1525,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VWP-01 Vuilwaterpomp 1</t>
+          <t>BKT-04 Brandklep toevoer traforuimte 1 K1-008 [?]</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1549,16 +1547,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VWP-02 Vuilwaterpomp 2 voeding</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>1</v>
-      </c>
+          <t>BKT-05 Brandklep toevoer traforuimte 2 K1-007 [?]</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -1573,14 +1569,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VWP-02 Vuilwaterpomp 2</t>
+          <t>BKA-01 Brandklep centrale retour [?]</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -1595,14 +1591,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VWP-02 Vuilwaterpomp 2</t>
+          <t>BKA-02 Brandklep retour LS-ruimte K1-005 [?]</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -1617,14 +1613,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VWP-02 Vuilwaterpomp 2</t>
+          <t>BKA-03 Brandklep retour schakelverdeelruimte K1-006 [?]</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -1639,14 +1635,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LA-02 Hoogniveau alarm [?]</t>
+          <t>BKA-04 Brandklep retour traforuimte 1 K1-008 [?]</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -1661,14 +1657,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LA-03 Laagniveau alarm [?]</t>
+          <t>BKA-05 Brandklep retour traforuimte 2 K1-007 [?]</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
+          <t>VWP-01 Vuilwaterpomp 1 voeding</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -1692,7 +1688,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -1707,14 +1703,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tracing terugmelding [?]</t>
+          <t>VWP-01 Vuilwaterpomp 1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -1729,16 +1725,14 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>VWP-03 Vuilwaterpomp 3 voeding</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1</v>
-      </c>
+          <t>VWP-01 Vuilwaterpomp 1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -1753,14 +1747,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VWP-03 Vuilwaterpomp 3</t>
+          <t>VWP-01 Vuilwaterpomp 1</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -1775,14 +1769,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VWP-03 Vuilwaterpomp 3</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>VWP-02 Vuilwaterpomp 2 voeding</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -1797,14 +1793,14 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VWP-03 Vuilwaterpomp 3</t>
+          <t>VWP-02 Vuilwaterpomp 2</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -1819,16 +1815,14 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VWP-04 Vuilwaterpomp 4 voeding</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>1</v>
-      </c>
+          <t>VWP-02 Vuilwaterpomp 2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -1843,14 +1837,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VWP-04 Vuilwaterpomp 4</t>
+          <t>VWP-02 Vuilwaterpomp 2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -1865,14 +1859,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VWP-04 Vuilwaterpomp 4</t>
+          <t>LA-02 Hoogniveau alarm [?]</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -1887,14 +1881,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VWP-04 Vuilwaterpomp 4</t>
+          <t>LA-03 Laagniveau alarm [?]</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -1909,19 +1903,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LA-01 Hoog/hoogniveau alarm [?]</t>
+          <t>Tracing voeding [?]</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 5G2,5 MT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>in TR</t>
+          <t>voeding doorlussen</t>
         </is>
       </c>
     </row>
@@ -1931,14 +1925,14 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LA-02 Hoogniveau alarm [?]</t>
+          <t>Tracing terugmelding [?]</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -1953,14 +1947,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LA-03 Laagniveau alarm [?]</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>VWP-03 Vuilwaterpomp 3 voeding</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -1975,16 +1971,14 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>1</v>
-      </c>
+          <t>VWP-03 Vuilwaterpomp 3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -1999,14 +1993,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tracing terugmelding [?]</t>
+          <t>VWP-03 Vuilwaterpomp 3</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2021,16 +2015,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp voeding</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>1</v>
-      </c>
+          <t>VWP-03 Vuilwaterpomp 3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2045,14 +2037,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>VWP-04 Vuilwaterpomp 4 voeding</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2067,14 +2061,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp</t>
+          <t>VWP-04 Vuilwaterpomp 4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2089,14 +2083,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp</t>
+          <t>VWP-04 Vuilwaterpomp 4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2111,14 +2105,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LA-01 Hoogniveau alarm [?]</t>
+          <t>VWP-04 Vuilwaterpomp 4</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2133,14 +2127,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LA-02 Laagniveau alarm [?]</t>
+          <t>LA-01 Hoog/hoogniveau alarm [?]</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2155,16 +2149,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>1</v>
-      </c>
+          <t>LA-02 Hoogniveau alarm [?]</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2179,14 +2171,14 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tracing terugmelding [?]</t>
+          <t>LA-03 Laagniveau alarm [?]</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2201,21 +2193,19 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp voeding</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>1</v>
-      </c>
+          <t>Tracing voeding [?]</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK HULT CCA 5G2,5 MT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>in TR</t>
+          <t>voeding doorlussen</t>
         </is>
       </c>
     </row>
@@ -2225,14 +2215,14 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp</t>
+          <t>Tracing terugmelding [?]</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2247,14 +2237,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HWP-01 Hemelwaterpomp</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>HWP-01 Hemelwaterpomp voeding</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2276,7 +2268,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2291,14 +2283,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>LA-01 Hoogniveau alarm [?]</t>
+          <t>HWP-01 Hemelwaterpomp</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2313,14 +2305,14 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LA-02 Laagniveau alarm [?]</t>
+          <t>HWP-01 Hemelwaterpomp</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2335,16 +2327,14 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>1</v>
-      </c>
+          <t>LA-01 Hoogniveau alarm [?]</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2359,14 +2349,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tracing terugmelding [?]</t>
+          <t>LA-02 Laagniveau alarm [?]</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2381,19 +2371,19 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RS-01 Reset storingen</t>
+          <t>Tracing voeding [?]</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 5G2,5 MT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>in TR</t>
+          <t>voeding doorlussen</t>
         </is>
       </c>
     </row>
@@ -2403,14 +2393,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SMC-01 Meldingen sprinklermeldventrale</t>
+          <t>Tracing terugmelding [?]</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2425,14 +2415,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SMC-01 Meldingen sprinklermeldventrale</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
+          <t>HWP-01 Hemelwaterpomp voeding</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2447,14 +2439,14 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SMC-01 Meldingen sprinklermeldventrale</t>
+          <t>HWP-01 Hemelwaterpomp</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2469,14 +2461,14 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>NW-01 Netwachter</t>
+          <t>HWP-01 Hemelwaterpomp</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2491,14 +2483,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>IA-01 Installatie automaten</t>
+          <t>HWP-01 Hemelwaterpomp</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2513,14 +2505,14 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SS-01 Stuurstroom</t>
+          <t>LA-01 Hoogniveau alarm [?]</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -2535,14 +2527,14 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>OSB-02 Overspanningsbeveiliging verdeelkast</t>
+          <t>LA-02 Laagniveau alarm [?]</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -2557,21 +2549,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>WD-01 Wateroverlastdetectie LS-ruimte K1-005 voeding</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>1</v>
-      </c>
+          <t>Tracing voeding [?]</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK HULT CCA 5G2,5 MT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>in TR</t>
+          <t>voeding doorlussen</t>
         </is>
       </c>
     </row>
@@ -2581,14 +2571,14 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>WD-01 Wateroverlastdetectie LS-ruimte K1-005</t>
+          <t>Tracing terugmelding [?]</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -2603,16 +2593,14 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WD-02 Wateroverlastdetectie NSA-ruimte K1-003 voeding</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>1</v>
-      </c>
+          <t>RS-01 Reset storingen</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -2627,14 +2615,14 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>WD-02 Wateroverlastdetectie NSA-ruimte K1-003</t>
+          <t>SMC-01 Meldingen sprinklermeldventrale</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -2649,16 +2637,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>WD-03 Wateroverlastdetectie sprinklerpompuitmte voeding</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>1</v>
-      </c>
+          <t>SMC-01 Meldingen sprinklermeldventrale</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -2673,14 +2659,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WD-03 Wateroverlastdetectie sprinklerpompuitmte</t>
+          <t>SMC-01 Meldingen sprinklermeldventrale</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>JOBA ST.STR B2CA HCHOZ 2X1 MT</t>
+          <t>DRAK CCA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -2689,31 +2675,257 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>97</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NW-01 Netwachter</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Onderstation algemeen</t>
+      <c r="A107" t="n">
+        <v>98</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>IA-01 Installatie automaten</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>in TR</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Brandmelding</t>
+          <t>SS-01 Stuurstroom</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>100</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>OSB-02 Overspanningsbeveiliging verdeelkast</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>101</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>WD-01 Wateroverlastdetectie LS-ruimte K1-005 voeding</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>102</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>WD-01 Wateroverlastdetectie LS-ruimte K1-005</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>103</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>WD-02 Wateroverlastdetectie NSA-ruimte K1-003 voeding</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>104</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>WD-02 Wateroverlastdetectie NSA-ruimte K1-003</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>105</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>WD-03 Wateroverlastdetectie sprinklerpompuitmte voeding</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>DRAK HULT CCA 3G2,5 HA500</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>106</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>WD-03 Wateroverlastdetectie sprinklerpompuitmte</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>DRAK CCA GY 2X0,8 MT</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>in TR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Onderstation algemeen</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>107</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Brandmelding</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>Kabel levering derde totaan RK, aansluiten kastzijde Erco</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/out_blind/cable_list_RK1.xlsx
+++ b/out_blind/cable_list_RK1.xlsx
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -558,7 +558,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -580,7 +580,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -604,7 +604,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -626,7 +626,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG CCA 3X2X0,8 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -648,7 +648,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -670,7 +670,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -692,7 +692,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -714,7 +714,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -736,7 +736,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -758,7 +758,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -780,7 +780,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -824,7 +824,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -846,7 +846,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -890,7 +890,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -912,7 +912,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -934,7 +934,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -956,7 +956,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -978,7 +978,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1024,7 +1024,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1046,7 +1046,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG CCA 3X2X0,8 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1068,7 +1068,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1090,7 +1090,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1112,7 +1112,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1156,7 +1156,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1178,7 +1178,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1200,7 +1200,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1222,7 +1222,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1266,7 +1266,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1290,7 +1290,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1312,7 +1312,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG CCA 3X2X0,8 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1334,7 +1334,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1356,7 +1356,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1378,7 +1378,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1400,7 +1400,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1422,7 +1422,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DRAK SIGK CCA 1X4X0,8 2502Q MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1444,7 +1444,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB CCA 4X0,8 HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1466,7 +1466,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1488,7 +1488,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1510,7 +1510,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -1532,7 +1532,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -1554,7 +1554,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -1576,7 +1576,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -1620,7 +1620,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -1642,7 +1642,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -1664,7 +1664,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -1710,7 +1710,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -1732,7 +1732,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -1754,7 +1754,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -1778,7 +1778,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -1800,7 +1800,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -1822,7 +1822,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -1844,7 +1844,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -1866,7 +1866,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -1888,7 +1888,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -1906,16 +1906,18 @@
           <t>Tracing voeding [?]</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 5G2,5 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>voeding doorlussen</t>
+          <t>in TR</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1934,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -1956,7 +1958,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -1978,7 +1980,7 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2000,7 +2002,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2022,7 +2024,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2046,7 +2048,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2068,7 +2070,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2090,7 +2092,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2112,7 +2114,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2134,7 +2136,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2156,7 +2158,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2178,7 +2180,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2196,16 +2198,18 @@
           <t>Tracing voeding [?]</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 5G2,5 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>voeding doorlussen</t>
+          <t>in TR</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2226,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2246,7 +2250,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2268,7 +2272,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2290,7 +2294,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2312,7 +2316,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2334,7 +2338,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2356,7 +2360,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2374,16 +2378,18 @@
           <t>Tracing voeding [?]</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 5G2,5 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>voeding doorlussen</t>
+          <t>in TR</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2406,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2424,7 +2430,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2446,7 +2452,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2468,7 +2474,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2490,7 +2496,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -2512,7 +2518,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -2534,7 +2540,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -2552,16 +2558,18 @@
           <t>Tracing voeding [?]</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 5G2,5 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>voeding doorlussen</t>
+          <t>in TR</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2586,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -2600,7 +2608,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -2622,7 +2630,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -2644,7 +2652,7 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -2666,7 +2674,7 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -2688,7 +2696,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -2710,7 +2718,7 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -2732,7 +2740,7 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -2754,7 +2762,7 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -2778,7 +2786,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -2800,7 +2808,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -2824,7 +2832,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -2846,7 +2854,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -2870,7 +2878,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>DRAK HULT CCA 3G2,5 HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -2892,7 +2900,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>DRAK CCA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">

--- a/out_blind/cable_list_RK1.xlsx
+++ b/out_blind/cable_list_RK1.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E687"/>
+  <dimension ref="A1:E693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -703,7 +703,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -3809,7 +3809,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Servomotor Open/Dicht voeding [?]</t>
+          <t>Servomotor Open/Dicht voeding</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -4543,20 +4543,18 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Servomotor Open/Dicht voeding [?]</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>1</v>
-      </c>
+          <t>Servomotor Open/Dicht</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Dakafvoerkap (nat)</t>
+          <t>Dakafvoerkap (droog)</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 4X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4564,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Afvoerventilator (geschakelde voeding (MBS+MS) / Vrijgave + Bedrijf + Storing) voeding</t>
+          <t>Servomotor Open/Dicht voeding</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -4574,7 +4572,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Afvoerventilator</t>
+          <t>Dakafvoerkap (nat)</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -4589,18 +4587,18 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Afvoerventilator (geschakelde voeding (MBS+MS) / Vrijgave + Bedrijf + Storing)</t>
+          <t>Servomotor Open/Dicht</t>
         </is>
       </c>
       <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Afvoerventilator</t>
+          <t>Dakafvoerkap (nat)</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
+          <t>DRAK B2CA GY 4X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -4654,18 +4652,20 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr"/>
+          <t>Afvoerventilator (geschakelde voeding (MBS+MS) / Vrijgave + Bedrijf + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>Afvoerventilator</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -4675,18 +4675,18 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Afvoerventilator (geschakelde voeding (MBS+MS) / Vrijgave + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Afvoerventilator</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -4702,7 +4702,7 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -4723,7 +4723,7 @@
       <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -4744,7 +4744,7 @@
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -4765,7 +4765,7 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -4786,7 +4786,7 @@
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -4807,7 +4807,7 @@
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -4828,7 +4828,7 @@
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -4849,7 +4849,7 @@
       <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -4870,7 +4870,7 @@
       <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -4891,7 +4891,7 @@
       <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -4912,7 +4912,7 @@
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -4927,13 +4927,13 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Water TT (temperatuuropnemer)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -4954,7 +4954,7 @@
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -4975,7 +4975,7 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -4996,7 +4996,7 @@
       <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -5011,13 +5011,13 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Water TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C220" t="inlineStr"/>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -5038,7 +5038,7 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -5059,7 +5059,7 @@
       <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -5080,7 +5080,7 @@
       <c r="C223" t="inlineStr"/>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -5101,7 +5101,7 @@
       <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -5122,7 +5122,7 @@
       <c r="C225" t="inlineStr"/>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -5143,7 +5143,7 @@
       <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -5164,7 +5164,7 @@
       <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -5179,13 +5179,13 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Water TT (temperatuuropnemer)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -5206,7 +5206,7 @@
       <c r="C229" t="inlineStr"/>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -5227,7 +5227,7 @@
       <c r="C230" t="inlineStr"/>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -5248,7 +5248,7 @@
       <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -5263,13 +5263,13 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Water TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr"/>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -5290,7 +5290,7 @@
       <c r="C233" t="inlineStr"/>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -5311,7 +5311,7 @@
       <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -5332,7 +5332,7 @@
       <c r="C235" t="inlineStr"/>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="C236" t="inlineStr"/>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -5374,7 +5374,7 @@
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -5395,7 +5395,7 @@
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -5416,7 +5416,7 @@
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -5431,13 +5431,13 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Water TT (temperatuuropnemer)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -5458,7 +5458,7 @@
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -5479,7 +5479,7 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -5500,7 +5500,7 @@
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -5515,13 +5515,13 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Water TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -5542,7 +5542,7 @@
       <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -5563,7 +5563,7 @@
       <c r="C246" t="inlineStr"/>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -5584,7 +5584,7 @@
       <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -5605,7 +5605,7 @@
       <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -5626,7 +5626,7 @@
       <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -5647,7 +5647,7 @@
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -5668,7 +5668,7 @@
       <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -5689,7 +5689,7 @@
       <c r="C252" t="inlineStr"/>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -5710,7 +5710,7 @@
       <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -5731,7 +5731,7 @@
       <c r="C254" t="inlineStr"/>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -5752,7 +5752,7 @@
       <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -5767,13 +5767,13 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Water TT (temperatuuropnemer)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -5794,7 +5794,7 @@
       <c r="C257" t="inlineStr"/>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -5815,7 +5815,7 @@
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -5836,7 +5836,7 @@
       <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -5851,13 +5851,13 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Water TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -5878,7 +5878,7 @@
       <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2-weg afsluiter GKW</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -5899,7 +5899,7 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Water TT GKW</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -5920,7 +5920,7 @@
       <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2-weg afsluiter CV</t>
+          <t>2-weg afsluiter GKW</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -5941,7 +5941,7 @@
       <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Water TT CV</t>
+          <t>Water TT GKW</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -5956,18 +5956,18 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Koelmachine Communicatief (Communication Protocol) incl. toebehoren MODbus koppeling</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Computair 1</t>
+          <t>2-weg afsluiter CV</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -5977,18 +5977,18 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Koelmachine Communicatief (Communication Protocol) incl. toebehoren MODbus koppeling</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Computair 2</t>
+          <t>Water TT CV</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -5998,18 +5998,18 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>QAA24Detector</t>
+          <t>Koelmachine Communicatief (Communication Protocol) incl. toebehoren MODbus koppeling</t>
         </is>
       </c>
       <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Computair 1</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
         </is>
       </c>
     </row>
@@ -6019,18 +6019,18 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>QFA2000Humidity sensor room 0-10V</t>
+          <t>Koelmachine Communicatief (Communication Protocol) incl. toebehoren MODbus koppeling</t>
         </is>
       </c>
       <c r="C268" t="inlineStr"/>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>Computair 2</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
         </is>
       </c>
     </row>
@@ -6040,20 +6040,18 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
-        </is>
-      </c>
-      <c r="C269" t="n">
-        <v>1</v>
-      </c>
+          <t>QAA24Detector</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr"/>
       <c r="D269" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6063,18 +6061,18 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
+          <t>QFA2000Humidity sensor room 0-10V</t>
         </is>
       </c>
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6084,18 +6082,20 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
-        </is>
-      </c>
-      <c r="C271" t="inlineStr"/>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Split-unit 1</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6105,13 +6105,13 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
         </is>
       </c>
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Split-unit 2</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
@@ -6126,18 +6126,18 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>QAA24Detector</t>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Split-unit 1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,18 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
-        </is>
-      </c>
-      <c r="C274" t="n">
-        <v>1</v>
-      </c>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr"/>
       <c r="D274" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Split-unit 2</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6170,18 +6168,18 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
+          <t>QAA24Detector</t>
         </is>
       </c>
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6191,18 +6189,20 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
-        </is>
-      </c>
-      <c r="C276" t="inlineStr"/>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1</v>
+      </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Split-unit 1</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6212,18 +6212,18 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>QAA24Detector</t>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
         </is>
       </c>
       <c r="C277" t="inlineStr"/>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6233,20 +6233,18 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
-        </is>
-      </c>
-      <c r="C278" t="n">
-        <v>1</v>
-      </c>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Split-unit 1</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6256,18 +6254,18 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
+          <t>QAA24Detector</t>
         </is>
       </c>
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6277,18 +6275,20 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
-        </is>
-      </c>
-      <c r="C280" t="inlineStr"/>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Split-unit 1</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6298,18 +6298,18 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>QAA24Detector</t>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
         </is>
       </c>
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6319,20 +6319,18 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
-        </is>
-      </c>
-      <c r="C282" t="n">
-        <v>1</v>
-      </c>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Split-unit 1</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6342,18 +6340,18 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
+          <t>QAA24Detector</t>
         </is>
       </c>
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6363,18 +6361,20 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
-        </is>
-      </c>
-      <c r="C284" t="inlineStr"/>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>1</v>
+      </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Split-unit 1</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6384,13 +6384,13 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
         </is>
       </c>
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Split-unit 2</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -6405,18 +6405,18 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>QAA24Detector</t>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Split-unit 1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6426,20 +6426,18 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
-        </is>
-      </c>
-      <c r="C287" t="n">
-        <v>1</v>
-      </c>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Split-unit 2</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6449,18 +6447,18 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
+          <t>QAA24Detector</t>
         </is>
       </c>
       <c r="C288" t="inlineStr"/>
       <c r="D288" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6470,18 +6468,20 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
-        </is>
-      </c>
-      <c r="C289" t="inlineStr"/>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>1</v>
+      </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Split-unit 1</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6491,13 +6491,13 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
         </is>
       </c>
       <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Split-unit 2</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -6512,18 +6512,18 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>QAA24Detector</t>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Split-unit 1</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6533,20 +6533,18 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
-        </is>
-      </c>
-      <c r="C292" t="n">
-        <v>1</v>
-      </c>
+          <t>Split-unit (Vrijgave + Bedrijf + Storing)</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr"/>
       <c r="D292" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Split-unit 2</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6556,18 +6554,18 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
+          <t>QAA24Detector</t>
         </is>
       </c>
       <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
-          <t>WOD versterker</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -6577,18 +6575,20 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Digitale koppeling (Communication Protocol) MODbus koppeling</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr"/>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm) voeding</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>1</v>
+      </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Rada regelsysteem</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6598,18 +6598,18 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Digitale koppeling (Communication Protocol) MODbus koppeling</t>
+          <t>Enkelvoudige versterker, inbouw (230VAC, incl. eindweerstand 120KΩ, potentiaalvrij contact, H120 x B105 x D35 mm)</t>
         </is>
       </c>
       <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
-          <t>Waterbehandeling</t>
+          <t>WOD versterker</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6619,20 +6619,18 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Geschakelde voeding (MBS+MS) 230VAC voeding [?]</t>
-        </is>
-      </c>
-      <c r="C296" t="n">
-        <v>1</v>
-      </c>
+          <t>Digitale koppeling (Communication Protocol) MODbus koppeling</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
-          <t>El. luchtgordijn</t>
+          <t>Rada regelsysteem</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -6642,18 +6640,18 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Geschakelde voeding (MBS+MS) 230VAC [?]</t>
+          <t>Digitale koppeling (Communication Protocol) MODbus koppeling</t>
         </is>
       </c>
       <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>El. luchtgordijn</t>
+          <t>Waterbehandeling</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -6663,18 +6661,20 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Blusgasinstalaltie (bedrijf / storing / alarm)</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr"/>
+          <t>Geschakelde voeding (MBS+MS) 230VAC voeding</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>1</v>
+      </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>MER/SER ruimte (2e)</t>
+          <t>El. luchtgordijn</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -6684,18 +6684,18 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Blusgasinstalaltie (bedrijf / storing / alarm)</t>
+          <t>Geschakelde voeding (MBS+MS) 230VAC</t>
         </is>
       </c>
       <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LS-ruimte (BG)</t>
+          <t>El. luchtgordijn</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 4X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6711,7 +6711,7 @@
       <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
-          <t>UPS schakelruimtes</t>
+          <t>MER/SER ruimte (2e)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -6726,18 +6726,18 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Bedienpanelen MODbus koppeling</t>
+          <t>Blusgasinstalaltie (bedrijf / storing / alarm)</t>
         </is>
       </c>
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Bedienpanelen</t>
+          <t>LS-ruimte (BG)</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6747,13 +6747,13 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>PV installatie [?]</t>
+          <t>Blusgasinstalaltie (bedrijf / storing / alarm)</t>
         </is>
       </c>
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>PV installatie</t>
+          <t>UPS schakelruimtes</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -6768,13 +6768,13 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>NSA 1 MODbus koppeling</t>
+          <t>Bedienpanelen MODbus koppeling</t>
         </is>
       </c>
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NSA 1</t>
+          <t>Bedienpanelen</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -6789,13 +6789,13 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>NSA 1</t>
+          <t>PV installatie [?]</t>
         </is>
       </c>
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NSA 1</t>
+          <t>PV installatie</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -6810,13 +6810,13 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>NSA 2 MODbus koppeling</t>
+          <t>NSA 1 MODbus koppeling</t>
         </is>
       </c>
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NSA 2</t>
+          <t>NSA 1</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -6831,13 +6831,13 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>NSA 2</t>
+          <t>NSA 1</t>
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NSA 2</t>
+          <t>NSA 1</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -6852,18 +6852,18 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>UPS 1 [?]</t>
+          <t>NSA 2 MODbus koppeling</t>
         </is>
       </c>
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>UPS 1</t>
+          <t>NSA 2</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -6873,13 +6873,13 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>UPS 2 [?]</t>
+          <t>NSA 2</t>
         </is>
       </c>
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>UPS 2</t>
+          <t>NSA 2</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -6894,18 +6894,18 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Zonwering (KNX) MODbus koppeling</t>
+          <t>UPS 1 [?]</t>
         </is>
       </c>
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Zonwering (KNX)</t>
+          <t>UPS 1</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6915,18 +6915,18 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Verlichting (DALI) MODbus koppeling</t>
+          <t>UPS 2 [?]</t>
         </is>
       </c>
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Verlichting (DALI)</t>
+          <t>UPS 2</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6936,18 +6936,18 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Alarmcentrale [?]</t>
+          <t>Zonwering (KNX) MODbus koppeling</t>
         </is>
       </c>
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Alarmcentrale</t>
+          <t>Zonwering (KNX)</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
         </is>
       </c>
     </row>
@@ -6957,13 +6957,13 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Winguard SMS MODbus koppeling</t>
+          <t>Verlichting (DALI) MODbus koppeling</t>
         </is>
       </c>
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Winguard SMS</t>
+          <t>Verlichting (DALI)</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -6978,18 +6978,18 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>3-fase kWh-meter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>Alarmcentrale [?]</t>
         </is>
       </c>
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>RK-4</t>
+          <t>Alarmcentrale</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -6999,18 +6999,18 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>3-fase kWh-meter Communicatief (Communication Protocol) MODbus koppeling</t>
+          <t>Winguard SMS MODbus koppeling</t>
         </is>
       </c>
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>RK-4</t>
+          <t>Winguard SMS</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>RK-2</t>
+          <t>RK-4</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -7047,7 +7047,7 @@
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>RK-2</t>
+          <t>RK-4</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
@@ -7068,7 +7068,7 @@
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>LWP</t>
+          <t>RK-2</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -7089,7 +7089,7 @@
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LWP</t>
+          <t>RK-2</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -7110,7 +7110,7 @@
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>LWP (bestaand)</t>
+          <t>LWP</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -7131,7 +7131,7 @@
       <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
-          <t>LWP (bestaand)</t>
+          <t>LWP</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -7152,7 +7152,7 @@
       <c r="C321" t="inlineStr"/>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LK-MER-A</t>
+          <t>LWP (bestaand)</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -7173,7 +7173,7 @@
       <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LK-MER-A</t>
+          <t>LWP (bestaand)</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -7194,7 +7194,7 @@
       <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
-          <t>KK NO BREAK 1</t>
+          <t>LK-MER-A</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -7215,7 +7215,7 @@
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>KK NO BREAK 1</t>
+          <t>LK-MER-A</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -7236,7 +7236,7 @@
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>KK NO BREAK 1</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -7257,7 +7257,7 @@
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>RK1</t>
+          <t>KK NO BREAK 1</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -7278,7 +7278,7 @@
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>KK-PV</t>
+          <t>RK1</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -7299,7 +7299,7 @@
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>KK-PV</t>
+          <t>RK1</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
@@ -7320,7 +7320,7 @@
       <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>RK5</t>
+          <t>KK-PV</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -7341,7 +7341,7 @@
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>RK5</t>
+          <t>KK-PV</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -7362,7 +7362,7 @@
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>RK3</t>
+          <t>RK5</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -7383,7 +7383,7 @@
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>RK3</t>
+          <t>RK5</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -7404,7 +7404,7 @@
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>LWP</t>
+          <t>RK3</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -7425,7 +7425,7 @@
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LWP</t>
+          <t>RK3</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -7446,7 +7446,7 @@
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LK-MER-B</t>
+          <t>LWP</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -7467,7 +7467,7 @@
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LK-MER-B</t>
+          <t>LWP</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
@@ -7488,7 +7488,7 @@
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>KK NO BREAK 2</t>
+          <t>LK-MER-B</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -7509,7 +7509,7 @@
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>KK NO BREAK 2</t>
+          <t>LK-MER-B</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -7524,18 +7524,18 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Brandklep</t>
+          <t>3-fase kWh-meter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Brandklep</t>
+          <t>KK NO BREAK 2</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -7545,18 +7545,18 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Brandklep</t>
+          <t>3-fase kWh-meter Communicatief (Communication Protocol) MODbus koppeling</t>
         </is>
       </c>
       <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>Brandklep</t>
+          <t>KK NO BREAK 2</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -7608,18 +7608,18 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering)</t>
+          <t>Brandklep</t>
         </is>
       </c>
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>Brandklep</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -7629,18 +7629,18 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering)</t>
+          <t>Brandklep</t>
         </is>
       </c>
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>Brandklep</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering) [?]</t>
+          <t>Overspanningsbeveiliging (Signalering)</t>
         </is>
       </c>
       <c r="C351" t="inlineStr"/>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering) [?]</t>
+          <t>Overspanningsbeveiliging (Signalering)</t>
         </is>
       </c>
       <c r="C352" t="inlineStr"/>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering)</t>
+          <t>Overspanningsbeveiliging (Signalering) [?]</t>
         </is>
       </c>
       <c r="C353" t="inlineStr"/>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering)</t>
+          <t>Overspanningsbeveiliging (Signalering) [?]</t>
         </is>
       </c>
       <c r="C354" t="inlineStr"/>
@@ -8028,13 +8028,13 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Reset storing RK</t>
+          <t>Overspanningsbeveiliging (Signalering)</t>
         </is>
       </c>
       <c r="C363" t="inlineStr"/>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>OSB</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging</t>
+          <t>Overspanningsbeveiliging (Signalering)</t>
         </is>
       </c>
       <c r="C364" t="inlineStr"/>
@@ -8070,13 +8070,13 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Brandweerschakelaars 2x voor TV &amp; AV (Aan / Auto / Uit) [?]</t>
+          <t>Reset storing RK</t>
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>BWS</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -8091,13 +8091,13 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Watermeter (Puls)</t>
+          <t>Overspanningsbeveiliging</t>
         </is>
       </c>
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Hoofdwatermeter</t>
+          <t>OSB</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -8112,13 +8112,13 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Gasmeter (Puls)</t>
+          <t>Brandweerschakelaars 2x voor TV &amp; AV (Aan / Auto / Uit) [?]</t>
         </is>
       </c>
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Hoofdgasmeter</t>
+          <t>BWS</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -8133,13 +8133,13 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Drukverhoging / Hydrofoor (Bedrijf + Storing)</t>
+          <t>Watermeter (Puls)</t>
         </is>
       </c>
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Hydrofoor</t>
+          <t>Hoofdwatermeter</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -8154,13 +8154,13 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Reset storing RK</t>
+          <t>Gasmeter (Puls)</t>
         </is>
       </c>
       <c r="C369" t="inlineStr"/>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>Hoofdgasmeter</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -8175,13 +8175,13 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging</t>
+          <t>Drukverhoging / Hydrofoor (Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>Hydrofoor</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -8280,13 +8280,13 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Brandweerschakelaars 2x voor TV &amp; AV (Aan / Auto / Uit) [?]</t>
+          <t>Reset storing RK</t>
         </is>
       </c>
       <c r="C375" t="inlineStr"/>
       <c r="D375" t="inlineStr">
         <is>
-          <t>BWS</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -8301,13 +8301,13 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Reset storing RK</t>
+          <t>Overspanningsbeveiliging</t>
         </is>
       </c>
       <c r="C376" t="inlineStr"/>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Reset</t>
+          <t>OSB</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -8322,13 +8322,13 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging</t>
+          <t>Brandweerschakelaars 2x voor TV &amp; AV (Aan / Auto / Uit) [?]</t>
         </is>
       </c>
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>BWS</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -8343,13 +8343,13 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Brandweerschakelaars 2x voor TV &amp; AV (Aan / Auto / Uit) [?]</t>
+          <t>Reset storing RK</t>
         </is>
       </c>
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>BWS</t>
+          <t>Reset</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
@@ -8364,20 +8364,18 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Priva Plus 100 datapoints 61 months 4g Connectivity Pack Edge Gateway voeding [?]</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>1</v>
-      </c>
+          <t>Overspanningsbeveiliging</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Edge Gateway</t>
+          <t>OSB</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8387,20 +8385,18 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Aansluitkast met overspanning beveiliging en voeding voeding</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>1</v>
-      </c>
+          <t>Brandweerschakelaars 2x voor TV &amp; AV (Aan / Auto / Uit) [?]</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Aansluitkast</t>
+          <t>BWS</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8410,18 +8406,20 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Aansluitkast met overspanning beveiliging en voeding MODbus koppeling</t>
-        </is>
-      </c>
-      <c r="C381" t="inlineStr"/>
+          <t>Priva Plus 100 datapoints 61 months 4g Connectivity Pack Edge Gateway voeding [?]</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>1</v>
+      </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Aansluitkast</t>
+          <t>Edge Gateway</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -8431,18 +8429,20 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Warmtepomp MODbus koppeling</t>
-        </is>
-      </c>
-      <c r="C382" t="inlineStr"/>
+          <t>Aansluitkast met overspanning beveiliging en voeding voeding</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>1</v>
+      </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Warmtepomp</t>
+          <t>Aansluitkast</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -8452,20 +8452,18 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>1</v>
-      </c>
+          <t>Aansluitkast met overspanning beveiliging en voeding MODbus koppeling</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Tracing</t>
+          <t>Aansluitkast</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -8475,18 +8473,18 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Warmtepomp MODbus koppeling</t>
         </is>
       </c>
       <c r="C384" t="inlineStr"/>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Warmtepomp</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
         </is>
       </c>
     </row>
@@ -8496,18 +8494,20 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
-        </is>
-      </c>
-      <c r="C385" t="inlineStr"/>
+          <t>Tracing voeding [?]</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>1</v>
+      </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Tracing</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -8517,18 +8517,18 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C386" t="inlineStr"/>
       <c r="D386" t="inlineStr">
         <is>
-          <t>3-weg afsluiter</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       <c r="C387" t="inlineStr"/>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Retourwater TT</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -8559,18 +8559,18 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Flowmeter (Puls)</t>
+          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
         </is>
       </c>
       <c r="C388" t="inlineStr"/>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Flowmeter</t>
+          <t>3-weg afsluiter</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8580,20 +8580,18 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
-        </is>
-      </c>
-      <c r="C389" t="n">
-        <v>1</v>
-      </c>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr"/>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Tracing</t>
+          <t>Retourwater TT</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -8603,18 +8601,18 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
+          <t>Flowmeter (Puls)</t>
         </is>
       </c>
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>3-weg afsluiter</t>
+          <t>Flowmeter</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8624,18 +8622,20 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
-        </is>
-      </c>
-      <c r="C391" t="inlineStr"/>
+          <t>Tracing voeding [?]</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>1</v>
+      </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Tracing</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 6X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -8645,18 +8645,18 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
+          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
         </is>
       </c>
       <c r="C392" t="inlineStr"/>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>3-weg afsluiter</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 6X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8792,18 +8792,18 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Warmtepomp MODbus koppeling</t>
+          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
         </is>
       </c>
       <c r="C399" t="inlineStr"/>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Warmtepomp</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
+          <t>DRAK B2CA GY 6X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8813,20 +8813,18 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Tracing voeding [?]</t>
-        </is>
-      </c>
-      <c r="C400" t="n">
-        <v>1</v>
-      </c>
+          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr"/>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Tracing</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 6X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8836,18 +8834,18 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
+          <t>Warmtepomp MODbus koppeling</t>
         </is>
       </c>
       <c r="C401" t="inlineStr"/>
       <c r="D401" t="inlineStr">
         <is>
-          <t>3-weg afsluiter</t>
+          <t>Warmtepomp</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>COMM U/UTP CAT6 CS34ZB HA305</t>
         </is>
       </c>
     </row>
@@ -8880,18 +8878,18 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
         </is>
       </c>
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>3-weg afsluiter</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8901,18 +8899,20 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
-        </is>
-      </c>
-      <c r="C404" t="inlineStr"/>
+          <t>Tracing voeding [?]</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>1</v>
+      </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Tracing</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -8922,18 +8922,18 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>3-weg afsluiter</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Retourwater TT</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
@@ -8964,18 +8964,18 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Flowmeter (Puls)</t>
+          <t>3-weg regelafsluiter Modulerend -&gt; Direct aangesloten op de warmtepomp</t>
         </is>
       </c>
       <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Flowmeter</t>
+          <t>3-weg afsluiter</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -8985,18 +8985,18 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C408" t="inlineStr"/>
       <c r="D408" t="inlineStr">
         <is>
-          <t>Warmtemeter</t>
+          <t>Retourwater TT</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9006,18 +9006,18 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Warmtemeter Communicatief (Communication Protocol) MODbus koppeling</t>
+          <t>Flowmeter (Puls)</t>
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Warmtemeter</t>
+          <t>Flowmeter</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9027,18 +9027,18 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C410" t="inlineStr"/>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Warmtemeter</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -9048,18 +9048,18 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Warmtemeter Communicatief (Communication Protocol) MODbus koppeling</t>
         </is>
       </c>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Warmtemeter</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -9069,18 +9069,18 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>QBE2003-P6 Pressure sensor liquid/gas</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Systeemdruk</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9090,18 +9090,18 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>AQB2005 Rel. Pressure connection set</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Aansluitset</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Via aansluitsnoer van 2 meter op meter</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9111,18 +9111,18 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Koudemeter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>QBE2003-P6 Pressure sensor liquid/gas</t>
         </is>
       </c>
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Koudemeter</t>
+          <t>Systeemdruk</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -9132,18 +9132,18 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Koudemeter Communicatief (Communication Protocol) MODbus koppeling</t>
+          <t>AQB2005 Rel. Pressure connection set</t>
         </is>
       </c>
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Koudemeter</t>
+          <t>Aansluitset</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>Via aansluitsnoer van 2 meter op meter</t>
         </is>
       </c>
     </row>
@@ -9153,18 +9153,18 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Koudemeter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C416" t="inlineStr"/>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Koudemeter</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -9174,18 +9174,18 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>Koudemeter Communicatief (Communication Protocol) MODbus koppeling</t>
         </is>
       </c>
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Koudemeter</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -9195,18 +9195,18 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>QBE2003-P6 Pressure sensor liquid/gas</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Systeemdruk</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9216,18 +9216,18 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>AQB2005 Rel. Pressure connection set</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C419" t="inlineStr"/>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Aansluitset</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Via aansluitsnoer van 2 meter op meter</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9237,18 +9237,18 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>QBE2003-P6 Pressure sensor liquid/gas</t>
         </is>
       </c>
       <c r="C420" t="inlineStr"/>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Warmtemeter</t>
+          <t>Systeemdruk</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -9258,18 +9258,18 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>AQB2005 Rel. Pressure connection set</t>
         </is>
       </c>
       <c r="C421" t="inlineStr"/>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Aansluitset</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>Via aansluitsnoer van 2 meter op meter</t>
         </is>
       </c>
     </row>
@@ -9279,18 +9279,18 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT (temperatuuropnemer)</t>
+          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C422" t="inlineStr"/>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Warmtemeter</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -9300,18 +9300,18 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Drukopnemer PT (Waterzijdig)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C423" t="inlineStr"/>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Systeemdruk</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9321,18 +9321,18 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Koudemeter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>Aanvoerwater TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C424" t="inlineStr"/>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Koudemeter</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9342,18 +9342,18 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Drukopnemer PT (Waterzijdig)</t>
         </is>
       </c>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Systeemdruk</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -9363,18 +9363,18 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT (temperatuuropnemer)</t>
+          <t>Koudemeter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Koudemeter</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -9384,18 +9384,18 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Drukopnemer PT (Waterzijdig)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Systeemdruk</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9405,18 +9405,18 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
+          <t>Aanvoerwater TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C428" t="inlineStr"/>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 6X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9426,18 +9426,18 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
+          <t>Drukopnemer PT (Waterzijdig)</t>
         </is>
       </c>
       <c r="C429" t="inlineStr"/>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Systeemdruk</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 6X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -9657,18 +9657,18 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
         </is>
       </c>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Warmtemeter</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK B2CA GY 6X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9678,18 +9678,18 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Warmtemeter Communicatief (Communication Protocol) MODbus koppeling</t>
+          <t>2-weg regelafsluiter Open/Dicht + 2 eindcontacten</t>
         </is>
       </c>
       <c r="C441" t="inlineStr"/>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Warmtemeter</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK B2CA GY 6X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9699,18 +9699,18 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C442" t="inlineStr"/>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Warmtemeter</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -9720,18 +9720,18 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Warmtemeter Communicatief (Communication Protocol) MODbus koppeling</t>
         </is>
       </c>
       <c r="C443" t="inlineStr"/>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Warmtemeter</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -9741,18 +9741,18 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C444" t="inlineStr"/>
       <c r="D444" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -9762,7 +9762,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C445" t="inlineStr"/>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9783,18 +9783,18 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C446" t="inlineStr"/>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9804,18 +9804,18 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>3-weg regelafsluiter Modulerend</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C447" t="inlineStr"/>
       <c r="D447" t="inlineStr">
         <is>
-          <t>3-weg afsluiter</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -9846,18 +9846,18 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
+          <t>3-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C449" t="inlineStr"/>
       <c r="D449" t="inlineStr">
         <is>
-          <t>Warmtemeter</t>
+          <t>3-weg afsluiter</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9888,18 +9888,18 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT (temperatuuropnemer)</t>
+          <t>Warmtemeter Communicatief (Communication Protocol) 24V voeding</t>
         </is>
       </c>
       <c r="C451" t="inlineStr"/>
       <c r="D451" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Warmtemeter</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -9930,18 +9930,18 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>3-weg regelafsluiter Modulerend</t>
+          <t>Aanvoerwater TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C453" t="inlineStr"/>
       <c r="D453" t="inlineStr">
         <is>
-          <t>3-weg afsluiter</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -9972,20 +9972,18 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C455" t="n">
-        <v>1</v>
-      </c>
+          <t>3-weg regelafsluiter Modulerend</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr"/>
       <c r="D455" t="inlineStr">
         <is>
-          <t>Transportpomp 1</t>
+          <t>3-weg afsluiter</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -9995,18 +9993,18 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C456" t="inlineStr"/>
       <c r="D456" t="inlineStr">
         <is>
-          <t>Transportpomp 1</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -10016,18 +10014,20 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>QBE3000-D6 Differential pressure sensor</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr"/>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>1</v>
+      </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>Drukverschilopnemer</t>
+          <t>Transportpomp 1</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -10037,18 +10037,18 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>AQB2002 Diff. Pressure connection set</t>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
         </is>
       </c>
       <c r="C458" t="inlineStr"/>
       <c r="D458" t="inlineStr">
         <is>
-          <t>Aansluitset</t>
+          <t>Transportpomp 1</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Via aansluitsnoer van 2 meter op meter</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -10058,18 +10058,18 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>QBE3000-D6 Differential pressure sensor</t>
         </is>
       </c>
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Drukverschilopnemer</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -10079,18 +10079,18 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>AQB2002 Diff. Pressure connection set</t>
         </is>
       </c>
       <c r="C460" t="inlineStr"/>
       <c r="D460" t="inlineStr">
         <is>
-          <t>Retourwater TT</t>
+          <t>Aansluitset</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>Via aansluitsnoer van 2 meter op meter</t>
         </is>
       </c>
     </row>
@@ -10100,20 +10100,18 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C461" t="n">
-        <v>1</v>
-      </c>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr"/>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Transportpomp 1</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10123,18 +10121,18 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C462" t="inlineStr"/>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Transportpomp 1</t>
+          <t>Retourwater TT</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10144,18 +10142,20 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>QBE3000-D6 Differential pressure sensor</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr"/>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>1</v>
+      </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Drukverschilopnemer</t>
+          <t>Transportpomp 1</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -10165,18 +10165,18 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>AQB2002 Diff. Pressure connection set</t>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
         </is>
       </c>
       <c r="C464" t="inlineStr"/>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Aansluitset</t>
+          <t>Transportpomp 1</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Via aansluitsnoer van 2 meter op meter</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -10186,18 +10186,18 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>QBE3000-D6 Differential pressure sensor</t>
         </is>
       </c>
       <c r="C465" t="inlineStr"/>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Retourwater TT</t>
+          <t>Drukverschilopnemer</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -10207,20 +10207,18 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C466" t="n">
-        <v>1</v>
-      </c>
+          <t>AQB2002 Diff. Pressure connection set</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr"/>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Transportpomp 2</t>
+          <t>Aansluitset</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>Via aansluitsnoer van 2 meter op meter</t>
         </is>
       </c>
     </row>
@@ -10230,18 +10228,18 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C467" t="inlineStr"/>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Transportpomp 2</t>
+          <t>Retourwater TT</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10251,18 +10249,20 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Drukverschilopnemer PdT (Waterzijdig)</t>
-        </is>
-      </c>
-      <c r="C468" t="inlineStr"/>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>1</v>
+      </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Drukverschilopnemer</t>
+          <t>Transportpomp 2</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -10272,18 +10272,18 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT (temperatuuropnemer)</t>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
         </is>
       </c>
       <c r="C469" t="inlineStr"/>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Aanvoerwater TT</t>
+          <t>Transportpomp 2</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -10293,18 +10293,18 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Retourwater TT (temperatuuropnemer)</t>
+          <t>Drukverschilopnemer PdT (Waterzijdig)</t>
         </is>
       </c>
       <c r="C470" t="inlineStr"/>
       <c r="D470" t="inlineStr">
         <is>
-          <t>Retourwater TT</t>
+          <t>Drukverschilopnemer</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -10314,20 +10314,18 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C471" t="n">
-        <v>1</v>
-      </c>
+          <t>Aanvoerwater TT (temperatuuropnemer)</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr"/>
       <c r="D471" t="inlineStr">
         <is>
-          <t>Transportpomp 2</t>
+          <t>Aanvoerwater TT</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10337,18 +10335,18 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
+          <t>Retourwater TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C472" t="inlineStr"/>
       <c r="D472" t="inlineStr">
         <is>
-          <t>Transportpomp 2</t>
+          <t>Retourwater TT</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10358,18 +10356,20 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Drukverschilopnemer PdT (Waterzijdig)</t>
-        </is>
-      </c>
-      <c r="C473" t="inlineStr"/>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>1</v>
+      </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>Drukverschilopnemer</t>
+          <t>Transportpomp 2</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -10379,18 +10379,18 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Retourwater TT (temperatuuropnemer)</t>
+          <t>Transportpomp met opgebouwde toerenregeling extern gestuurd (Vrijgave + Sturing + Storing)</t>
         </is>
       </c>
       <c r="C474" t="inlineStr"/>
       <c r="D474" t="inlineStr">
         <is>
-          <t>Retourwater TT</t>
+          <t>Transportpomp 2</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>3x2x0,8</t>
         </is>
       </c>
     </row>
@@ -10400,18 +10400,18 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>QAA24 Detector</t>
+          <t>Drukverschilopnemer PdT (Waterzijdig)</t>
         </is>
       </c>
       <c r="C475" t="inlineStr"/>
       <c r="D475" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Drukverschilopnemer</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK B2CA 1X4X0,8 2502Q MT</t>
         </is>
       </c>
     </row>
@@ -10421,13 +10421,13 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>QFA2000 Humidity sensor room 0-10V</t>
+          <t>Retourwater TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C476" t="inlineStr"/>
       <c r="D476" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>Retourwater TT</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -10442,13 +10442,13 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>QPA2000 CO2 sensor room 0-10V</t>
+          <t>QAA24 Detector</t>
         </is>
       </c>
       <c r="C477" t="inlineStr"/>
       <c r="D477" t="inlineStr">
         <is>
-          <t>Ruimte CO2</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
@@ -10463,18 +10463,18 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>QFA2000 Humidity sensor room 0-10V</t>
         </is>
       </c>
       <c r="C478" t="inlineStr"/>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10484,18 +10484,18 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>QPA2000 CO2 sensor room 0-10V</t>
         </is>
       </c>
       <c r="C479" t="inlineStr"/>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte CO2</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10505,18 +10505,18 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Ruimte TT (temperatuuropnemer)</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C480" t="inlineStr"/>
       <c r="D480" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -10526,18 +10526,18 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Ruimte RV (vochtopnemer)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -10547,13 +10547,13 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>CO2 sensor</t>
+          <t>Ruimte TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Ruimte CO2</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -10568,18 +10568,18 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Ruimte RV (vochtopnemer)</t>
         </is>
       </c>
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10589,13 +10589,13 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>QAA24 Detector</t>
+          <t>CO2 sensor</t>
         </is>
       </c>
       <c r="C484" t="inlineStr"/>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Ruimte CO2</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -10610,18 +10610,18 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>QFA2000 Humidity sensor room 0-10V</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C485" t="inlineStr"/>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -10631,13 +10631,13 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>QPA2000 CO2 sensor room 0-10V</t>
+          <t>QAA24 Detector</t>
         </is>
       </c>
       <c r="C486" t="inlineStr"/>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Ruimte CO2</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -10652,18 +10652,18 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>QFA2000 Humidity sensor room 0-10V</t>
         </is>
       </c>
       <c r="C487" t="inlineStr"/>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10673,18 +10673,18 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>QPA2000 CO2 sensor room 0-10V</t>
         </is>
       </c>
       <c r="C488" t="inlineStr"/>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte CO2</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10694,18 +10694,18 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>Ruimte TT (temperatuuropnemer)</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C489" t="inlineStr"/>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -10715,18 +10715,18 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>Ruimte RV (vochtopnemer)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C490" t="inlineStr"/>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -10736,13 +10736,13 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>CO2 sensor</t>
+          <t>Ruimte TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C491" t="inlineStr"/>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Ruimte CO2</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -10757,18 +10757,18 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Ruimte RV (vochtopnemer)</t>
         </is>
       </c>
       <c r="C492" t="inlineStr"/>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10778,13 +10778,13 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>QAA24 Detector</t>
+          <t>CO2 sensor</t>
         </is>
       </c>
       <c r="C493" t="inlineStr"/>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>Ruimte CO2</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -10799,18 +10799,18 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>QFA2000 Humidity sensor room 0-10V</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C494" t="inlineStr"/>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -10820,13 +10820,13 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>QPA2000 CO2 sensor room 0-10V</t>
+          <t>QAA24 Detector</t>
         </is>
       </c>
       <c r="C495" t="inlineStr"/>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Ruimte CO2</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -10841,18 +10841,18 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>QFA2000 Humidity sensor room 0-10V</t>
         </is>
       </c>
       <c r="C496" t="inlineStr"/>
       <c r="D496" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10862,18 +10862,18 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>QPA2000 CO2 sensor room 0-10V</t>
         </is>
       </c>
       <c r="C497" t="inlineStr"/>
       <c r="D497" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte CO2</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10883,18 +10883,18 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>Ruimte TT (temperatuuropnemer)</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C498" t="inlineStr"/>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -10904,18 +10904,18 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>Ruimte RV (vochtopnemer)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C499" t="inlineStr"/>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Ruimte RV</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -10925,13 +10925,13 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>CO2 sensor</t>
+          <t>Ruimte TT (temperatuuropnemer)</t>
         </is>
       </c>
       <c r="C500" t="inlineStr"/>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Ruimte CO2</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
@@ -10946,18 +10946,18 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Ruimte RV (vochtopnemer)</t>
         </is>
       </c>
       <c r="C501" t="inlineStr"/>
       <c r="D501" t="inlineStr">
         <is>
-          <t>2-weg afsluiter</t>
+          <t>Ruimte RV</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10967,18 +10967,18 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering)</t>
+          <t>CO2 sensor</t>
         </is>
       </c>
       <c r="C502" t="inlineStr"/>
       <c r="D502" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>Ruimte CO2</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -10988,18 +10988,18 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>Overspanningsbeveiliging (Signalering)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C503" t="inlineStr"/>
       <c r="D503" t="inlineStr">
         <is>
-          <t>OSB</t>
+          <t>2-weg afsluiter</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -11639,18 +11639,18 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>Fijnstof</t>
+          <t>Overspanningsbeveiliging (Signalering)</t>
         </is>
       </c>
       <c r="C534" t="inlineStr"/>
       <c r="D534" t="inlineStr">
         <is>
-          <t>Fijnstof</t>
+          <t>OSB</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -11660,18 +11660,18 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>WatchGas - TOX Point 2000 - O2</t>
+          <t>Overspanningsbeveiliging (Signalering)</t>
         </is>
       </c>
       <c r="C535" t="inlineStr"/>
       <c r="D535" t="inlineStr">
         <is>
-          <t>Zuurstof (O2)</t>
+          <t>OSB</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -11681,13 +11681,13 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>WatchGas - TOX Point 2000 - CO</t>
+          <t>Fijnstof</t>
         </is>
       </c>
       <c r="C536" t="inlineStr"/>
       <c r="D536" t="inlineStr">
         <is>
-          <t>Koolmonoxide (CO)</t>
+          <t>Fijnstof</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
@@ -11702,13 +11702,13 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>AIR XD Real Time Dust Monitor</t>
+          <t>WatchGas - TOX Point 2000 - O2</t>
         </is>
       </c>
       <c r="C537" t="inlineStr"/>
       <c r="D537" t="inlineStr">
         <is>
-          <t>Stikstofoxiden (NOx)</t>
+          <t>Zuurstof (O2)</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -11723,13 +11723,13 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>WatchGas - TOX Point 2000 - NH3 - Low range</t>
+          <t>WatchGas - TOX Point 2000 - CO</t>
         </is>
       </c>
       <c r="C538" t="inlineStr"/>
       <c r="D538" t="inlineStr">
         <is>
-          <t>Ammoniak (NH3)</t>
+          <t>Koolmonoxide (CO)</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -11744,13 +11744,13 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>1xSBPMF-F1EU + 5x SPM Flex CC-U XP Mineral Acids (90)</t>
+          <t>AIR XD Real Time Dust Monitor</t>
         </is>
       </c>
       <c r="C539" t="inlineStr"/>
       <c r="D539" t="inlineStr">
         <is>
-          <t>Zwavelzuur (H2SO4)</t>
+          <t>Stikstofoxiden (NOx)</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
@@ -11765,13 +11765,13 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Watchgas - VOCpoint - PID 10.6eV 0.01-20 ppm</t>
+          <t>WatchGas - TOX Point 2000 - NH3 - Low range</t>
         </is>
       </c>
       <c r="C540" t="inlineStr"/>
       <c r="D540" t="inlineStr">
         <is>
-          <t>Liq. Petroleum Gas (LPG)</t>
+          <t>Ammoniak (NH3)</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -11786,13 +11786,13 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>WatchGas - LEL Point 2000</t>
+          <t>1xSBPMF-F1EU + 5x SPM Flex CC-U XP Mineral Acids (90)</t>
         </is>
       </c>
       <c r="C541" t="inlineStr"/>
       <c r="D541" t="inlineStr">
         <is>
-          <t>Aardgas/LNG (LEL)</t>
+          <t>Zwavelzuur (H2SO4)</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
@@ -11807,13 +11807,13 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>VOC/VOS (PID)</t>
+          <t>Watchgas - VOCpoint - PID 10.6eV 0.01-20 ppm</t>
         </is>
       </c>
       <c r="C542" t="inlineStr"/>
       <c r="D542" t="inlineStr">
         <is>
-          <t>VOC/VOS (PID)</t>
+          <t>Liq. Petroleum Gas (LPG)</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -11828,13 +11828,13 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
+          <t>WatchGas - LEL Point 2000</t>
         </is>
       </c>
       <c r="C543" t="inlineStr"/>
       <c r="D543" t="inlineStr">
         <is>
-          <t>Aanzuig TT</t>
+          <t>Aardgas/LNG (LEL)</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -11849,18 +11849,18 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>GCA126.1E Damper actuator</t>
+          <t>VOC/VOS (PID)</t>
         </is>
       </c>
       <c r="C544" t="inlineStr"/>
       <c r="D544" t="inlineStr">
         <is>
-          <t>Buitenluchtklep</t>
+          <t>VOC/VOS (PID)</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -11870,18 +11870,18 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>GBB161.1E Damper actuator</t>
+          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
         </is>
       </c>
       <c r="C545" t="inlineStr"/>
       <c r="D545" t="inlineStr">
         <is>
-          <t>By-pass klep</t>
+          <t>Aanzuig TT</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -11891,18 +11891,18 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>GCA126.1E Damper actuator</t>
         </is>
       </c>
       <c r="C546" t="inlineStr"/>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>Buitenluchtklep</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -11912,18 +11912,18 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>GBB161.1E Damper actuator</t>
         </is>
       </c>
       <c r="C547" t="inlineStr"/>
       <c r="D547" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>By-pass klep</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -11933,20 +11933,18 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Warmtewiel (Vrijgave + Sturing + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C548" t="n">
-        <v>1</v>
-      </c>
+          <t>QBM3020-5 Diff. pressure sensor</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr"/>
       <c r="D548" t="inlineStr">
         <is>
-          <t>Warmtewiel</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -11956,18 +11954,18 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Warmtewiel (Vrijgave + Sturing + Storing)</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C549" t="inlineStr"/>
       <c r="D549" t="inlineStr">
         <is>
-          <t>Warmtewiel</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -11977,18 +11975,20 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
-        </is>
-      </c>
-      <c r="C550" t="inlineStr"/>
+          <t>Warmtewiel (Vrijgave + Sturing + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C550" t="n">
+        <v>1</v>
+      </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>Warmtewiel</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -11998,20 +11998,18 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C551" t="n">
-        <v>1</v>
-      </c>
+          <t>Warmtewiel (Vrijgave + Sturing + Storing)</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr"/>
       <c r="D551" t="inlineStr">
         <is>
-          <t>Toevoerventilator</t>
+          <t>Warmtewiel</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12021,18 +12019,18 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C552" t="inlineStr"/>
       <c r="D552" t="inlineStr">
         <is>
-          <t>Toevoerventilator</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12042,18 +12040,20 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
-        </is>
-      </c>
-      <c r="C553" t="inlineStr"/>
+          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C553" t="n">
+        <v>1</v>
+      </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (+)</t>
+          <t>Toevoerventilator</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -12063,18 +12063,18 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C554" t="inlineStr"/>
       <c r="D554" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (+)</t>
+          <t>Toevoerventilator</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12084,20 +12084,18 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C555" t="n">
-        <v>1</v>
-      </c>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr"/>
       <c r="D555" t="inlineStr">
         <is>
-          <t>Circulatiepomp (+)</t>
+          <t>2-weg afsluiter (+)</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -12107,18 +12105,18 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing)</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C556" t="inlineStr"/>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Circulatiepomp (+)</t>
+          <t>2-weg afsluiter (+)</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12128,18 +12126,20 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr"/>
+          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C557" t="n">
+        <v>1</v>
+      </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Retourwater TT (+)</t>
+          <t>Circulatiepomp (+)</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -12149,18 +12149,18 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>QAF81.6 Thermostat</t>
+          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing)</t>
         </is>
       </c>
       <c r="C558" t="inlineStr"/>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Vorsthermostaat</t>
+          <t>Circulatiepomp (+)</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -12170,18 +12170,18 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C559" t="inlineStr"/>
       <c r="D559" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (-)</t>
+          <t>Retourwater TT (+)</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12191,18 +12191,18 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>QAF81.6 Thermostat</t>
         </is>
       </c>
       <c r="C560" t="inlineStr"/>
       <c r="D560" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (-)</t>
+          <t>Vorsthermostaat</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12212,18 +12212,18 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C561" t="inlineStr"/>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Retourwater TT (-)</t>
+          <t>2-weg afsluiter (-)</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -12233,20 +12233,18 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C562" t="n">
-        <v>1</v>
-      </c>
+          <t>2-weg regelafsluiter Modulerend</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr"/>
       <c r="D562" t="inlineStr">
         <is>
-          <t>El. Naverwarmer</t>
+          <t>2-weg afsluiter (-)</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12256,18 +12254,18 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing)</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C563" t="inlineStr"/>
       <c r="D563" t="inlineStr">
         <is>
-          <t>El. Naverwarmer</t>
+          <t>Retourwater TT (-)</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12277,18 +12275,20 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr"/>
+          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C564" t="n">
+        <v>1</v>
+      </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>El. Naverwarmer</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -12298,18 +12298,18 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C565" t="inlineStr"/>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>El. Naverwarmer</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -12340,18 +12340,18 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
+          <t>GBB141.1E Damper actuator</t>
         </is>
       </c>
       <c r="C567" t="inlineStr"/>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Inblaas TT</t>
+          <t>Luchtklepservo</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12361,18 +12361,18 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>GBB141.1E Damper actuator</t>
         </is>
       </c>
       <c r="C568" t="inlineStr"/>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Inblaas PT</t>
+          <t>Luchtklepservo</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12382,18 +12382,18 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>VAV klep (0-10V sturing)</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C569" t="inlineStr"/>
       <c r="D569" t="inlineStr">
         <is>
-          <t>VAV toevoer</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12403,13 +12403,13 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>QPM1104 Duct sensor CO2</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C570" t="inlineStr"/>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Retour CO2</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
@@ -12424,18 +12424,18 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>VAV klep (0-10V sturing)</t>
+          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
         </is>
       </c>
       <c r="C571" t="inlineStr"/>
       <c r="D571" t="inlineStr">
         <is>
-          <t>VAV afvoer</t>
+          <t>Inblaas TT</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12451,7 +12451,7 @@
       <c r="C572" t="inlineStr"/>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Retour PT</t>
+          <t>Inblaas PT</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
@@ -12466,18 +12466,18 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
+          <t>VAV klep (0-10V sturing)</t>
         </is>
       </c>
       <c r="C573" t="inlineStr"/>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Retour TT</t>
+          <t>VAV toevoer</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12487,13 +12487,13 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>QPM1104 Duct sensor CO2</t>
         </is>
       </c>
       <c r="C574" t="inlineStr"/>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>Retour CO2</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
@@ -12508,18 +12508,18 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>VAV klep (0-10V sturing)</t>
         </is>
       </c>
       <c r="C575" t="inlineStr"/>
       <c r="D575" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>VAV afvoer</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12529,13 +12529,13 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C576" t="inlineStr"/>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>Retour PT</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
@@ -12550,20 +12550,18 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C577" t="n">
-        <v>1</v>
-      </c>
+          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr"/>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Afvoerventilator</t>
+          <t>Retour TT</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12573,18 +12571,18 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C578" t="inlineStr"/>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Afvoerventilator</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12594,18 +12592,18 @@
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>GCA126.1E Damper actuator</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C579" t="inlineStr"/>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Buitenluchtklep</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12615,13 +12613,13 @@
       </c>
       <c r="B580" t="inlineStr">
         <is>
-          <t>Fijnstof</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C580" t="inlineStr"/>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Fijnstof</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
@@ -12636,18 +12634,20 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>WatchGas - TOX Point 2000 - O2</t>
-        </is>
-      </c>
-      <c r="C581" t="inlineStr"/>
+          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C581" t="n">
+        <v>1</v>
+      </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Zuurstof (O2)</t>
+          <t>Afvoerventilator</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -12657,18 +12657,18 @@
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>WatchGas - TOX Point 2000 - CO</t>
+          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C582" t="inlineStr"/>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Koolmonoxide (CO)</t>
+          <t>Afvoerventilator</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12678,18 +12678,18 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>AIR XD Real Time Dust Monitor</t>
+          <t>GCA126.1E Damper actuator</t>
         </is>
       </c>
       <c r="C583" t="inlineStr"/>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Stikstofoxiden (NOx)</t>
+          <t>Buitenluchtklep</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12699,13 +12699,13 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>WatchGas - TOX Point 2000 - NH3 - Low range</t>
+          <t>Fijnstof</t>
         </is>
       </c>
       <c r="C584" t="inlineStr"/>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Ammoniak (NH3)</t>
+          <t>Fijnstof</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -12720,13 +12720,13 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>1xSBPMF-F1EU + 5x SPM Flex CC-U XP Mineral Acids (90)</t>
+          <t>WatchGas - TOX Point 2000 - O2</t>
         </is>
       </c>
       <c r="C585" t="inlineStr"/>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Zwavelzuur (H2SO4)</t>
+          <t>Zuurstof (O2)</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
@@ -12741,13 +12741,13 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>Watchgas - VOCpoint - PID 10.6eV 0.01-20 ppm</t>
+          <t>WatchGas - TOX Point 2000 - CO</t>
         </is>
       </c>
       <c r="C586" t="inlineStr"/>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Liq. Petroleum Gas (LPG)</t>
+          <t>Koolmonoxide (CO)</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
@@ -12762,13 +12762,13 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>WatchGas - LEL Point 2000</t>
+          <t>AIR XD Real Time Dust Monitor</t>
         </is>
       </c>
       <c r="C587" t="inlineStr"/>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Aardgas/LNG (LEL)</t>
+          <t>Stikstofoxiden (NOx)</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
@@ -12783,13 +12783,13 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>VOC/VOS (PID)</t>
+          <t>WatchGas - TOX Point 2000 - NH3 - Low range</t>
         </is>
       </c>
       <c r="C588" t="inlineStr"/>
       <c r="D588" t="inlineStr">
         <is>
-          <t>VOC/VOS (PID)</t>
+          <t>Ammoniak (NH3)</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -12804,13 +12804,13 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
+          <t>1xSBPMF-F1EU + 5x SPM Flex CC-U XP Mineral Acids (90)</t>
         </is>
       </c>
       <c r="C589" t="inlineStr"/>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Aanzuig TT</t>
+          <t>Zwavelzuur (H2SO4)</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
@@ -12825,18 +12825,18 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>GCA126.1E Damper actuator</t>
+          <t>Watchgas - VOCpoint - PID 10.6eV 0.01-20 ppm</t>
         </is>
       </c>
       <c r="C590" t="inlineStr"/>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Buitenluchtklep</t>
+          <t>Liq. Petroleum Gas (LPG)</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12846,18 +12846,18 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>GBB161.1E Damper actuator</t>
+          <t>WatchGas - LEL Point 2000</t>
         </is>
       </c>
       <c r="C591" t="inlineStr"/>
       <c r="D591" t="inlineStr">
         <is>
-          <t>By-pass klep</t>
+          <t>Aardgas/LNG (LEL)</t>
         </is>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12867,13 +12867,13 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>VOC/VOS (PID)</t>
         </is>
       </c>
       <c r="C592" t="inlineStr"/>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>VOC/VOS (PID)</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -12888,13 +12888,13 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
         </is>
       </c>
       <c r="C593" t="inlineStr"/>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>Aanzuig TT</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -12909,20 +12909,18 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Warmtewiel (Vrijgave + Sturing + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C594" t="n">
-        <v>1</v>
-      </c>
+          <t>GCA126.1E Damper actuator</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr"/>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Warmtewiel</t>
+          <t>Buitenluchtklep</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 3G2,5 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12932,18 +12930,18 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Warmtewiel (Vrijgave + Sturing + Storing)</t>
+          <t>GBB161.1E Damper actuator</t>
         </is>
       </c>
       <c r="C595" t="inlineStr"/>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Warmtewiel</t>
+          <t>By-pass klep</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -12953,13 +12951,13 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C596" t="inlineStr"/>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
@@ -12974,20 +12972,18 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C597" t="n">
-        <v>1</v>
-      </c>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr"/>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Toevoerventilator</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -12997,18 +12993,20 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
-        </is>
-      </c>
-      <c r="C598" t="inlineStr"/>
+          <t>Warmtewiel (Vrijgave + Sturing + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C598" t="n">
+        <v>1</v>
+      </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Toevoerventilator</t>
+          <t>Warmtewiel</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
+          <t>DRAK HULT B2CA 3G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -13018,18 +13016,18 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
+          <t>Warmtewiel (Vrijgave + Sturing + Storing)</t>
         </is>
       </c>
       <c r="C599" t="inlineStr"/>
       <c r="D599" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (+)</t>
+          <t>Warmtewiel</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13039,18 +13037,18 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C600" t="inlineStr"/>
       <c r="D600" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (+)</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13060,7 +13058,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing) voeding</t>
+          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
         </is>
       </c>
       <c r="C601" t="n">
@@ -13068,7 +13066,7 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Circulatiepomp (+)</t>
+          <t>Toevoerventilator</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
@@ -13083,18 +13081,18 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing)</t>
+          <t>Toevoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C602" t="inlineStr"/>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Circulatiepomp (+)</t>
+          <t>Toevoerventilator</t>
         </is>
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13104,18 +13102,18 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C603" t="inlineStr"/>
       <c r="D603" t="inlineStr">
         <is>
-          <t>Retourwater TT (+)</t>
+          <t>2-weg afsluiter (+)</t>
         </is>
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -13125,18 +13123,18 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>QAF81.6 Thermostat</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C604" t="inlineStr"/>
       <c r="D604" t="inlineStr">
         <is>
-          <t>Vorsthermostaat</t>
+          <t>2-weg afsluiter (+)</t>
         </is>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13146,18 +13144,20 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
-        </is>
-      </c>
-      <c r="C605" t="inlineStr"/>
+          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C605" t="n">
+        <v>1</v>
+      </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (-)</t>
+          <t>Circulatiepomp (+)</t>
         </is>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -13167,18 +13167,18 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>2-weg regelafsluiter Modulerend</t>
+          <t>Circulatiepomp met opgebouwde toerenregeling (Vrijgave + Storing)</t>
         </is>
       </c>
       <c r="C606" t="inlineStr"/>
       <c r="D606" t="inlineStr">
         <is>
-          <t>2-weg afsluiter (-)</t>
+          <t>Circulatiepomp (+)</t>
         </is>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>1x4x0,8</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       <c r="C607" t="inlineStr"/>
       <c r="D607" t="inlineStr">
         <is>
-          <t>Retourwater TT (-)</t>
+          <t>Retourwater TT (+)</t>
         </is>
       </c>
       <c r="E607" t="inlineStr">
@@ -13209,20 +13209,18 @@
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C608" t="n">
-        <v>1</v>
-      </c>
+          <t>QAF81.6 Thermostat</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr"/>
       <c r="D608" t="inlineStr">
         <is>
-          <t>El. Naverwarmer</t>
+          <t>Vorsthermostaat</t>
         </is>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13232,18 +13230,18 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing)</t>
+          <t>2-weg regelafsluiter Modulerend MODbus koppeling</t>
         </is>
       </c>
       <c r="C609" t="inlineStr"/>
       <c r="D609" t="inlineStr">
         <is>
-          <t>El. Naverwarmer</t>
+          <t>2-weg afsluiter (-)</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -13253,18 +13251,18 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>2-weg regelafsluiter Modulerend</t>
         </is>
       </c>
       <c r="C610" t="inlineStr"/>
       <c r="D610" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>2-weg afsluiter (-)</t>
         </is>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13274,13 +13272,13 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
+          <t>TM65-A 100mm Display Dompel/Kanaaltemperatuuropnemer 0-10V/4-20mA met instelbaar meetbereik</t>
         </is>
       </c>
       <c r="C611" t="inlineStr"/>
       <c r="D611" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>Retourwater TT (-)</t>
         </is>
       </c>
       <c r="E611" t="inlineStr">
@@ -13295,18 +13293,20 @@
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>QBM3020-5 Diff. pressure sensor</t>
-        </is>
-      </c>
-      <c r="C612" t="inlineStr"/>
+          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C612" t="n">
+        <v>1</v>
+      </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>El. Naverwarmer</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -13316,18 +13316,18 @@
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
+          <t>Elektrische verwarmer Modulerend (Sturing + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C613" t="inlineStr"/>
       <c r="D613" t="inlineStr">
         <is>
-          <t>Inblaas TT</t>
+          <t>El. Naverwarmer</t>
         </is>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
       <c r="C614" t="inlineStr"/>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Inblaas PT</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -13358,13 +13358,13 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>VAV klep (0-10V sturing)</t>
+          <t>GBB141.1E Damper actuator</t>
         </is>
       </c>
       <c r="C615" t="inlineStr"/>
       <c r="D615" t="inlineStr">
         <is>
-          <t>VAV toevoer</t>
+          <t>Luchtklepservo</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
@@ -13379,18 +13379,18 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>QPM1104 Duct sensor CO2</t>
+          <t>GBB141.1E Damper actuator</t>
         </is>
       </c>
       <c r="C616" t="inlineStr"/>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Retour CO2</t>
+          <t>Luchtklepservo</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13400,18 +13400,18 @@
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>VAV klep (0-10V sturing)</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C617" t="inlineStr"/>
       <c r="D617" t="inlineStr">
         <is>
-          <t>VAV afvoer</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       <c r="C618" t="inlineStr"/>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Retour PT</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
@@ -13448,7 +13448,7 @@
       <c r="C619" t="inlineStr"/>
       <c r="D619" t="inlineStr">
         <is>
-          <t>Retour TT</t>
+          <t>Inblaas TT</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -13469,7 +13469,7 @@
       <c r="C620" t="inlineStr"/>
       <c r="D620" t="inlineStr">
         <is>
-          <t>Vuilfiltersignalering</t>
+          <t>Inblaas PT</t>
         </is>
       </c>
       <c r="E620" t="inlineStr">
@@ -13484,18 +13484,18 @@
       </c>
       <c r="B621" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>VAV klep (0-10V sturing)</t>
         </is>
       </c>
       <c r="C621" t="inlineStr"/>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>VAV toevoer</t>
         </is>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13505,13 +13505,13 @@
       </c>
       <c r="B622" t="inlineStr">
         <is>
-          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
+          <t>QPM1104 Duct sensor CO2</t>
         </is>
       </c>
       <c r="C622" t="inlineStr"/>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Kanaal TT/RV</t>
+          <t>Retour CO2</t>
         </is>
       </c>
       <c r="E622" t="inlineStr">
@@ -13526,20 +13526,18 @@
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
-        </is>
-      </c>
-      <c r="C623" t="n">
-        <v>1</v>
-      </c>
+          <t>VAV klep (0-10V sturing)</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr"/>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Afvoerventilator</t>
+          <t>VAV afvoer</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>DRAK HULT B2CA 4G2,5 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13549,18 +13547,18 @@
       </c>
       <c r="B624" t="inlineStr">
         <is>
-          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C624" t="inlineStr"/>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Afvoerventilator</t>
+          <t>Retour PT</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13570,18 +13568,18 @@
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>GCA126.1E Damper actuator</t>
+          <t>MWTM-I 0,4m Display instelbaar meetbereik Gemiddeldewaarde temperatuuropnemer actief</t>
         </is>
       </c>
       <c r="C625" t="inlineStr"/>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Buitenluchtklep</t>
+          <t>Retour TT</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13591,13 +13589,13 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>Sensor Link cable 10 m with flying leads</t>
+          <t>QBM3020-5 Diff. pressure sensor</t>
         </is>
       </c>
       <c r="C626" t="inlineStr"/>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Vloertemperatuur</t>
+          <t>Vuilfiltersignalering</t>
         </is>
       </c>
       <c r="E626" t="inlineStr">
@@ -13612,18 +13610,18 @@
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>RAK-TW.1000HB</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C627" t="inlineStr"/>
       <c r="D627" t="inlineStr">
         <is>
-          <t>Max. thermostaat</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13633,18 +13631,18 @@
       </c>
       <c r="B628" t="inlineStr">
         <is>
-          <t>NovoCon S, Digitale Servomotor voor AB-QM DN 10-32 MODbus koppeling</t>
+          <t>KFTF-20-I Display 4...20mA Kanaalopnemer RV/ temperatuur actief ±1,8% nauwk, Pleuroform, TYR 2</t>
         </is>
       </c>
       <c r="C628" t="inlineStr"/>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Novocon-S</t>
+          <t>Kanaal TT/RV</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13654,18 +13652,20 @@
       </c>
       <c r="B629" t="inlineStr">
         <is>
-          <t>AB-QM DN 15 LF, Buitendraad, PN25, Drukgecompenseerde regelafsluiter</t>
-        </is>
-      </c>
-      <c r="C629" t="inlineStr"/>
+          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing) voeding</t>
+        </is>
+      </c>
+      <c r="C629" t="n">
+        <v>1</v>
+      </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Regelafsluiter</t>
+          <t>Afvoerventilator</t>
         </is>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK HULT B2CA 4G2,5 MT</t>
         </is>
       </c>
     </row>
@@ -13675,18 +13675,18 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>NovoCon S, Digitale Servomotor voor AB-QM DN 10-32 MODbus koppeling</t>
+          <t>Afvoerventilator (vaste voeding (inst.automaat) / Sturing + Bedrijf + Storing)</t>
         </is>
       </c>
       <c r="C630" t="inlineStr"/>
       <c r="D630" t="inlineStr">
         <is>
-          <t>Novocon-S</t>
+          <t>Afvoerventilator</t>
         </is>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK AFG B2CA 3X2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -13696,13 +13696,13 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>AB-QM DN 15 LF, Buitendraad, PN25, Drukgecompenseerde regelafsluiter</t>
+          <t>GCA126.1E Damper actuator</t>
         </is>
       </c>
       <c r="C631" t="inlineStr"/>
       <c r="D631" t="inlineStr">
         <is>
-          <t>Regelafsluiter</t>
+          <t>Buitenluchtklep</t>
         </is>
       </c>
       <c r="E631" t="inlineStr">
@@ -13717,18 +13717,18 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>NovoCon S, Digitale Servomotor voor AB-QM DN 10-32 MODbus koppeling</t>
+          <t>Sensor Link cable 10 m with flying leads</t>
         </is>
       </c>
       <c r="C632" t="inlineStr"/>
       <c r="D632" t="inlineStr">
         <is>
-          <t>Novocon-S</t>
+          <t>Vloertemperatuur</t>
         </is>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -13738,18 +13738,18 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>AB-QM DN 15 LF, Buitendraad, PN25, Drukgecompenseerde regelafsluiter</t>
+          <t>RAK-TW.1000HB</t>
         </is>
       </c>
       <c r="C633" t="inlineStr"/>
       <c r="D633" t="inlineStr">
         <is>
-          <t>Regelafsluiter</t>
+          <t>Max. thermostaat</t>
         </is>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14221,18 +14221,18 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
+          <t>NovoCon S, Digitale Servomotor voor AB-QM DN 10-32 MODbus koppeling</t>
         </is>
       </c>
       <c r="C656" t="inlineStr"/>
       <c r="D656" t="inlineStr">
         <is>
-          <t>6-weg ChangeOver</t>
+          <t>Novocon-S</t>
         </is>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -14242,13 +14242,13 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
+          <t>AB-QM DN 15 LF, Buitendraad, PN25, Drukgecompenseerde regelafsluiter</t>
         </is>
       </c>
       <c r="C657" t="inlineStr"/>
       <c r="D657" t="inlineStr">
         <is>
-          <t>6-weg ChangeOver</t>
+          <t>Regelafsluiter</t>
         </is>
       </c>
       <c r="E657" t="inlineStr">
@@ -14263,18 +14263,18 @@
       </c>
       <c r="B658" t="inlineStr">
         <is>
-          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
+          <t>NovoCon S, Digitale Servomotor voor AB-QM DN 10-32 MODbus koppeling</t>
         </is>
       </c>
       <c r="C658" t="inlineStr"/>
       <c r="D658" t="inlineStr">
         <is>
-          <t>6-weg ChangeOver</t>
+          <t>Novocon-S</t>
         </is>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -14284,13 +14284,13 @@
       </c>
       <c r="B659" t="inlineStr">
         <is>
-          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
+          <t>AB-QM DN 15 LF, Buitendraad, PN25, Drukgecompenseerde regelafsluiter</t>
         </is>
       </c>
       <c r="C659" t="inlineStr"/>
       <c r="D659" t="inlineStr">
         <is>
-          <t>6-weg ChangeOver</t>
+          <t>Regelafsluiter</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -14305,18 +14305,18 @@
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
+          <t>NovoCon S, Digitale Servomotor voor AB-QM DN 10-32 MODbus koppeling</t>
         </is>
       </c>
       <c r="C660" t="inlineStr"/>
       <c r="D660" t="inlineStr">
         <is>
-          <t>6-weg ChangeOver</t>
+          <t>Novocon-S</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 8X0,8 MT</t>
+          <t>BMS Cable 2x2x24AWG - R1319 - B2ca s1,d0,a1 Violet HA500</t>
         </is>
       </c>
     </row>
@@ -14326,13 +14326,13 @@
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
+          <t>AB-QM DN 15 LF, Buitendraad, PN25, Drukgecompenseerde regelafsluiter</t>
         </is>
       </c>
       <c r="C661" t="inlineStr"/>
       <c r="D661" t="inlineStr">
         <is>
-          <t>6-weg ChangeOver</t>
+          <t>Regelafsluiter</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
@@ -14515,18 +14515,18 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>Sensor Link cable 10 m with flying leads</t>
+          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
         </is>
       </c>
       <c r="C670" t="inlineStr"/>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Vloertemperatuur</t>
+          <t>6-weg ChangeOver</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14536,18 +14536,18 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>RAK-TW.1000HB</t>
+          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
         </is>
       </c>
       <c r="C671" t="inlineStr"/>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Max. thermostaat</t>
+          <t>6-weg ChangeOver</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14557,18 +14557,18 @@
       </c>
       <c r="B672" t="inlineStr">
         <is>
-          <t>Sensor Link cable 10 m with flying leads</t>
+          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
         </is>
       </c>
       <c r="C672" t="inlineStr"/>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Vloertemperatuur</t>
+          <t>6-weg ChangeOver</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14578,18 +14578,18 @@
       </c>
       <c r="B673" t="inlineStr">
         <is>
-          <t>RAK-TW.1000HB</t>
+          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
         </is>
       </c>
       <c r="C673" t="inlineStr"/>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Max. thermostaat</t>
+          <t>6-weg ChangeOver</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>DRAK B2CA GY 2X0,8 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14599,18 +14599,18 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>Fancoil unit</t>
+          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
         </is>
       </c>
       <c r="C674" t="inlineStr"/>
       <c r="D674" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>6-weg ChangeOver</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14620,18 +14620,18 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>QAA24</t>
+          <t>ChangeOver6 DN 15, gemotoriseerde 6-weg kogelafsluiter</t>
         </is>
       </c>
       <c r="C675" t="inlineStr"/>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Ruimte TT</t>
+          <t>6-weg ChangeOver</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>DRAK B2CA GY 8X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14641,18 +14641,18 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>Fancoil unit</t>
+          <t>Sensor Link cable 10 m with flying leads</t>
         </is>
       </c>
       <c r="C676" t="inlineStr"/>
       <c r="D676" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>Vloertemperatuur</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -14662,18 +14662,18 @@
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>Fancoil unit</t>
+          <t>RAK-TW.1000HB</t>
         </is>
       </c>
       <c r="C677" t="inlineStr"/>
       <c r="D677" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>Max. thermostaat</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14683,18 +14683,18 @@
       </c>
       <c r="B678" t="inlineStr">
         <is>
-          <t>VAV box (incl. opgebouwde VAV regelaar 0-10V)</t>
+          <t>Sensor Link cable 10 m with flying leads</t>
         </is>
       </c>
       <c r="C678" t="inlineStr"/>
       <c r="D678" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>Vloertemperatuur</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -14704,18 +14704,18 @@
       </c>
       <c r="B679" t="inlineStr">
         <is>
-          <t>VAV box (incl. opgebouwde VAV regelaar 0-10V)</t>
+          <t>RAK-TW.1000HB</t>
         </is>
       </c>
       <c r="C679" t="inlineStr"/>
       <c r="D679" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>Max. thermostaat</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK B2CA GY 2X0,8 MT</t>
         </is>
       </c>
     </row>
@@ -14725,13 +14725,13 @@
       </c>
       <c r="B680" t="inlineStr">
         <is>
-          <t>VAV box (incl. opgebouwde VAV regelaar 0-10V)</t>
+          <t>Fancoil unit</t>
         </is>
       </c>
       <c r="C680" t="inlineStr"/>
       <c r="D680" t="inlineStr">
         <is>
-          <t>VAV</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
@@ -14746,18 +14746,18 @@
       </c>
       <c r="B681" t="inlineStr">
         <is>
-          <t>Fancoil unit</t>
+          <t>QAA24</t>
         </is>
       </c>
       <c r="C681" t="inlineStr"/>
       <c r="D681" t="inlineStr">
         <is>
-          <t>FCU</t>
+          <t>Ruimte TT</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
         </is>
       </c>
     </row>
@@ -14788,18 +14788,18 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>QAM2120.200 (1)</t>
+          <t>Fancoil unit</t>
         </is>
       </c>
       <c r="C683" t="inlineStr"/>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Inblaas TT</t>
+          <t>FCU</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
@@ -14809,41 +14809,167 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>QAM2120.200 (2)</t>
+          <t>VAV box (incl. opgebouwde VAV regelaar 0-10V)</t>
         </is>
       </c>
       <c r="C684" t="inlineStr"/>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Inblaas TT</t>
+          <t>VAV</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="n">
+        <v>674</v>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>VAV box (incl. opgebouwde VAV regelaar 0-10V)</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr"/>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>VAV</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr"/>
-      <c r="B686" s="2" t="inlineStr">
-        <is>
-          <t>Onderstation algemeen</t>
+      <c r="A686" t="n">
+        <v>675</v>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>VAV box (incl. opgebouwde VAV regelaar 0-10V)</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr"/>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>VAV</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
+          <t>Fancoil unit</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr"/>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>FCU</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="n">
+        <v>677</v>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Fancoil unit</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr"/>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>FCU</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>RAK SIGN KAB B2CA 4X0,8 HA500</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="n">
+        <v>678</v>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>QAM2120.200 (1)</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr"/>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Inblaas TT</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="n">
+        <v>679</v>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>QAM2120.200 (2)</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr"/>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Inblaas TT</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>DRAK SIGK B2CA 1X2X0,8 2501 MT</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr"/>
+      <c r="B692" s="2" t="inlineStr">
+        <is>
+          <t>Onderstation algemeen</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="n">
+        <v>680</v>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
           <t>Brandmelding</t>
         </is>
       </c>
-      <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr">
+      <c r="C693" t="inlineStr"/>
+      <c r="D693" t="inlineStr"/>
+      <c r="E693" t="inlineStr">
         <is>
           <t>Kabel levering derde totaan RK, aansluiten kastzijde Erco</t>
         </is>
